--- a/ThaiPrint-Pricing-Calculator-v2.xlsx
+++ b/ThaiPrint-Pricing-Calculator-v2.xlsx
@@ -13,8 +13,9 @@
     <sheet name="PrintCost" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Spoilage" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="PaperPrice" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PaperCutting" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="QuickSelect" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PlasticPrice" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PaperCutting" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="QuickSelect" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,9 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;฿&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -202,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -294,6 +297,21 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3682,6 +3700,456 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>วิธีคิดราคาแผ่นพลาสติก (ขายเป็น กก. → คิดต่อแผ่น)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>สูตร: น้ำหนัก(กรัม) = กว้าง(ซม.) × ยาว(ซม.) × (ความหนา_มม. ÷ 10) × ค่าถ่วง   |   ราคา/แผ่น = น้ำหนัก ÷ 1000 × ราคา/กก.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ค่าถ่วงจำเพาะ (Density) ของพลาสติก</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>พลาสติก</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ค่าถ่วง (g/cm³)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PVC (แข็ง)</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>นิยมทำการ์ด แข็งแรง</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ใส คงรูปดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>เบา ลอยน้ำ ถูกสุด</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>เปราะ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ทนความร้อน</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>เครื่องคิดราคาแผ่นพลาสติก (กรอกช่องเหลือง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>กว้าง (ซม.)</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="C14" s="17" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>ยาว (ซม.)</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="C15" s="17" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>ความหนา (มม.)</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C16" s="17" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>ค่าถ่วง (g/cm³)</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C17" s="17" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>ราคา/กก. (บาท)</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="C18" s="17" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>จำนวน (แผ่น)</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C19" s="17" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>กำไร % (markup)</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ผลคำนวณ (อัตโนมัติ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ความหนา (ซม.)</t>
+        </is>
+      </c>
+      <c r="B23" s="36">
+        <f>B16/10</f>
+        <v/>
+      </c>
+      <c r="C23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>น้ำหนัก 1 แผ่น (กรัม)</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>B14*B15*B23*B17</f>
+        <v/>
+      </c>
+      <c r="C24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ราคาต้นทุน/แผ่น (บาท)</t>
+        </is>
+      </c>
+      <c r="B25" s="37">
+        <f>B24/1000*B18</f>
+        <v/>
+      </c>
+      <c r="C25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ราคาขาย/แผ่น (+กำไร) (บาท)</t>
+        </is>
+      </c>
+      <c r="B26" s="38">
+        <f>B25*(1+B20/100)</f>
+        <v/>
+      </c>
+      <c r="C26" s="17" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>น้ำหนักรวม (กก.)</t>
+        </is>
+      </c>
+      <c r="B27" s="7">
+        <f>B24*B19/1000</f>
+        <v/>
+      </c>
+      <c r="C27" s="17" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ราคาต้นทุนรวม (บาท)</t>
+        </is>
+      </c>
+      <c r="B28" s="7">
+        <f>B25*B19</f>
+        <v/>
+      </c>
+      <c r="C28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ราคาขายรวม (บาท)</t>
+        </is>
+      </c>
+      <c r="B29" s="39">
+        <f>B26*B19</f>
+        <v/>
+      </c>
+      <c r="C29" s="17" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ตารางสำเร็จ — PVC (ค่าถ่วง 1.40, ราคา 80 บาท/กก.) ราคาต้นทุน/แผ่น</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ขนาด</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>0.2 มม.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>0.3 มม.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0.4 มม.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>0.5 มม.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>A4 (21x29.7)</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>A3 (29.7x42)</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>31x43 นิ้ว (78.74x109.22)</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>38.53</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>48.16</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>25x36 นิ้ว (63.5x91.44)</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>32.52</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>หมายเหตุ: ตารางนี้เป็นราคาต้นทุน ราคาขายให้คูณ 1.20 (บวกกำไร 20%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B26:C26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
@@ -4198,7 +4666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/ThaiPrint-Pricing-Calculator-v2.xlsx
+++ b/ThaiPrint-Pricing-Calculator-v2.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Quotation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Machines" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PrintCost" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Spoilage" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="PaperPrice" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PlasticPrice" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PaperCutting" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="QuickSelect" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="StickerCalc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Quotation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Machines" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PrintCost" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Spoilage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PaperPrice" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PlasticPrice" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PaperCutting" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="QuickSelect" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,11 +25,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="&quot;฿&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="168" formatCode="&quot;฿&quot;#,##0.0000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -205,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -267,6 +269,15 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1759,7 +1770,979 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quick Select — แนะนำเครื่อง / วิธีพิมพ์ / จำนวนสี</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. แนะนำวิธีพิมพ์ตามจำนวนสั่ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>จำนวนสั่ง</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>วิธีแนะนำ</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>เหตุผล</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>&lt; 500 ชิ้น</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Work-and-Turn</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ค่าเพลทประหยัดครึ่งหนึ่ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>500–2,000 ชิ้น</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Work-and-Turn</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>ยังประหยัดได้ชัดเจน</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2,001–5,000 ชิ้น</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Work-and-Turn / Sheetwise</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>พิจารณาตามคุณภาพ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>&gt; 5,000 ชิ้น</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Sheetwise</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Registration ดีกว่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2. แนะนำเครื่องตามจำนวนสี</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>งาน</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>เครื่องที่แนะนำ</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>1–2 สี</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>GTO52, MO</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>4 สี (CMYK)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>GTO52, MO, SM74, XL106</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>5+ สี + Pantone/Coating</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>GTO52, MO, SM74</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>5+ unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>พิมพ์ 2 ด้านรอบเดียว</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>MOVP, SM74-2P, XL106-2P</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Perfector</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>3. แนะนำเครื่องตามขนาดกระดาษ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>กระดาษ</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>เครื่องที่รองรับ</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>≤ 36×52 ซม. (A3+)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>GTO 46, GTO 52, SM52</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>งานเล็ก ปริมาณน้อย</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>≤ 48×65 ซม.</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>MO / MOVP</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>B2 นิยมในไทย (ตัด 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>≤ 52×74 ซม.</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>SX52</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>24"×35" หรือ 25"×36"</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>SM74 / CD102 / XL106</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>เหมาะงาน A4 ไม่เสียเศษ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>≤ 53×74 ซม.</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SM74 / SX74</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>B2+ สมรรถนะสูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>≤ 53×75 ซม.</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>XL75</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>B2+ XL series</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>≤ 72×102 ซม.</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>CD102 / SX102</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>≤ 75×106 ซม.</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>XL106 / Komori S40</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>B1 สมรรถนะสูงสุด</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ งาน A4 ห้ามใช้กระดาษ 31×43 (เสียเศษมาก) — ใช้ 24×35 หรือ 25×36 แทน</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A30:C30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>คิดราคาสติกเกอร์/ฉลาก — Offset อุตสาหกรรม (โมเดลล่าสุด: ค่าพิมพ์/ใบ + เรต UV + วัสดุเผื่อเสีย)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>🟡 ช่องเหลือง = กรอก  |  🟢 เขียว = ผลคำนวณ  |  ตรงกับเว็บ calculator (ระบบ Offset อุตสาหกรรม → สติกเกอร์/ฉลาก)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ข้อมูลงาน (กรอกช่องสีเหลือง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>ชื่องาน</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>สติกเกอร์ PVC 10×10</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="17" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>กว้าง (ซม.)</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>ยาว (ซม.)</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="17" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>จำนวนสี (รวมหน้า+หลัง)</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="17" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>จำนวน (ชิ้น)</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="17" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>ประเภทหมึก</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="17" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>ขนาดเพลท</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>ตัด 4</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="17" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>ราคาวัสดุ (บาท/ตร.ซม.)</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="17" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>💡 ชนิดหมึกตามวัสดุ: สติกเกอร์ PVC/PP/PET/ฟอยล์ + แผ่นพลาสติก = UV | กระดาษอาร์ท/สติกเกอร์กระดาษ = Conventional | ตัด 4 = MO 65×48 | ตัด 2 = SM74 74×53</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>เลย์ชิ้นงาน + จำนวนใบพิมพ์ (อัตโนมัติ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>ใบพิมพ์ กว้าง (ซม.)</t>
+        </is>
+      </c>
+      <c r="B16" s="18">
+        <f>IF(B11="ตัด 2",74,65)</f>
+        <v/>
+      </c>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="17" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ใบพิมพ์ ยาว (ซม.)</t>
+        </is>
+      </c>
+      <c r="B17" s="18">
+        <f>IF(B11="ตัด 2",53,48)</f>
+        <v/>
+      </c>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="17" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>พื้นที่พิมพ์ กว้าง (− Gripper 1.2)</t>
+        </is>
+      </c>
+      <c r="B18" s="18">
+        <f>B16-1.2</f>
+        <v/>
+      </c>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="17" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>พื้นที่พิมพ์ ยาว (− Side Lay 0.7)</t>
+        </is>
+      </c>
+      <c r="B19" s="18">
+        <f>B17-0.7</f>
+        <v/>
+      </c>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="17" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>footprint กว้าง (+ Bleed 0.6)</t>
+        </is>
+      </c>
+      <c r="B20" s="18">
+        <f>B6+0.6</f>
+        <v/>
+      </c>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="17" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>footprint ยาว (+ Bleed 0.6)</t>
+        </is>
+      </c>
+      <c r="B21" s="18">
+        <f>B7+0.6</f>
+        <v/>
+      </c>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>ชิ้น/ใบ — แนวปกติ</t>
+        </is>
+      </c>
+      <c r="B22" s="19">
+        <f>INT(B18/B20)*INT(B19/B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="17" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ชิ้น/ใบ — หมุน 90°</t>
+        </is>
+      </c>
+      <c r="B23" s="19">
+        <f>INT(B18/B21)*INT(B19/B20)</f>
+        <v/>
+      </c>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ชิ้น/ใบพิมพ์ (nUp = เลือกค่ามาก)</t>
+        </is>
+      </c>
+      <c r="B24" s="19">
+        <f>MAX(B22,B23)</f>
+        <v/>
+      </c>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ใบพิมพ์ขั้นต่ำ</t>
+        </is>
+      </c>
+      <c r="B25" s="19">
+        <f>CEILING(B9/B24,1)</f>
+        <v/>
+      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>อัตราเผื่อเสีย (%) — UV10/4สี8/1สี3/อื่น5</t>
+        </is>
+      </c>
+      <c r="B26" s="24">
+        <f>IF(B10="UV",10,IF(B8&gt;=4,8,IF(B8&lt;=1,3,5)))</f>
+        <v/>
+      </c>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="17" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ใบพิมพ์เผื่อเสีย</t>
+        </is>
+      </c>
+      <c r="B27" s="19">
+        <f>CEILING(B25*B26/100,1)</f>
+        <v/>
+      </c>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="17" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ใบพิมพ์รวม (คิดค่าพิมพ์)</t>
+        </is>
+      </c>
+      <c r="B28" s="19">
+        <f>B25+B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ชิ้นเผื่อเสีย (= ใบเผื่อเสีย × nUp)</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>B27*B24</f>
+        <v/>
+      </c>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="17" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ราคา (อัตโนมัติ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>ค่าเพลท/สี (ตัด 4=300, ตัด 2=600)</t>
+        </is>
+      </c>
+      <c r="B32" s="19">
+        <f>IF(B11="ตัด 2",600,300)</f>
+        <v/>
+      </c>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="17" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>ค่าเพลทรวม (× จำนวนสี)</t>
+        </is>
+      </c>
+      <c r="B33" s="7">
+        <f>B32*B8</f>
+        <v/>
+      </c>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>เหมา/สี (flat rate)</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>IF(B11="ตัด 4",IF(B10="UV",1500,900),IF(B10="UV",2000,1200))</f>
+        <v/>
+      </c>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="17" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>ช่วงเหมา ขอบบน (ใบ)</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>IF(AND(B11="ตัด 4",B10="UV"),1000,10000)</f>
+        <v/>
+      </c>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="17" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>ส่วนเกิน (บาท/ใบ/สี)</t>
+        </is>
+      </c>
+      <c r="B36" s="18">
+        <f>IF(B11="ตัด 4",IF(B10="UV",1,0.1),IF(B10="UV",1.5,0.2))</f>
+        <v/>
+      </c>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="17" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>ใบส่วนเกิน</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>MAX(B28-B35,0)</f>
+        <v/>
+      </c>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="17" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>ค่าพิมพ์รวม = (เหมา + เกิน×อัตรา) × สี</t>
+        </is>
+      </c>
+      <c r="B38" s="7">
+        <f>(B34+B37*B36)*B8</f>
+        <v/>
+      </c>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="17" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>พื้นที่ชิ้น (ตร.ซม.)</t>
+        </is>
+      </c>
+      <c r="B39" s="7">
+        <f>B6*B7</f>
+        <v/>
+      </c>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="17" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ค่าวัสดุ = ราคา/ตร.ซม. × พื้นที่ × (จำนวน + เผื่อเสีย)</t>
+        </is>
+      </c>
+      <c r="B40" s="7">
+        <f>B12*B39*(B9+B29)</f>
+        <v/>
+      </c>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="17" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>สรุปราคา</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>ราคารวม (ค่าเพลท + ค่าพิมพ์ + ค่าวัสดุ)</t>
+        </is>
+      </c>
+      <c r="B43" s="21">
+        <f>B33+B38+B40</f>
+        <v/>
+      </c>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>ราคาต่อชิ้น</t>
+        </is>
+      </c>
+      <c r="B44" s="25">
+        <f>B43/B9</f>
+        <v/>
+      </c>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>ตัวอย่างตรวจสอบ: PVC UV 10×10 ซม. 4 สี 10,000 ชิ้น → nUp 24, ใบขั้นต่ำ 417, เผื่อเสีย 42 → 459 ใบ | ค่าเพลท 1,200 + ค่าพิมพ์ 6,000 (UV ตัด 4 เหมา) + ค่าวัสดุ 4,403.20 = ฿11,603.20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="41">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="B34:E34"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Conventional,UV"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"ตัด 4,ตัด 2"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1776,28 +2759,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>บริษัท ไทยพริ้นท์ อินเตอร์กรุ๊ป จำกัด</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>ThaiPrint Intergroup Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ใบเสนอราคา / QUOTATION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>ลูกค้า:</t>
         </is>
@@ -1807,18 +2790,18 @@
           <t>________________________</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>วันที่:</t>
         </is>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="30">
         <f>TODAY()</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>ที่อยู่:</t>
         </is>
@@ -1828,7 +2811,7 @@
           <t>________________________</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>เลขที่:</t>
         </is>
@@ -1840,7 +2823,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>โทร:</t>
         </is>
@@ -2108,80 +3091,80 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="n"/>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="A28" s="31" t="n"/>
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>ยอดรวมต้นทุน</t>
         </is>
       </c>
       <c r="C28" s="16" t="n"/>
       <c r="D28" s="17" t="n"/>
-      <c r="E28" s="30">
+      <c r="E28" s="33">
         <f>SUM(E24:E26)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="31" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>ราคาเสนอ (รวมทั้งหมด)</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>
       <c r="D29" s="17" t="n"/>
-      <c r="E29" s="32">
+      <c r="E29" s="35">
         <f>Calculator!B71</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>ราคาต่อชิ้น</t>
         </is>
       </c>
       <c r="C30" s="16" t="n"/>
       <c r="D30" s="17" t="n"/>
-      <c r="E30" s="33">
+      <c r="E30" s="36">
         <f>Calculator!B72</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>หมายเหตุ:</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>• ราคานี้ยังไม่รวม VAT 7%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>• ราคาเสนอมีผลภายใน 30 วัน</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>• ระยะเวลาส่งมอบ 7-14 วันทำการหลังยืนยันแบบ</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>ผู้เสนอราคา</t>
         </is>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>ผู้อนุมัติ</t>
         </is>
@@ -2233,7 +3216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2778,7 +3761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3028,7 +4011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3242,7 +4225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3694,7 +4677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3755,7 +4738,7 @@
           <t>PVC (แข็ง)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="38" t="n">
         <v>1.4</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3770,7 +4753,7 @@
           <t>PET</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="38" t="n">
         <v>1.38</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -3785,7 +4768,7 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="38" t="n">
         <v>0.905</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -3800,7 +4783,7 @@
           <t>PS</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="38" t="n">
         <v>1.05</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3815,7 +4798,7 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="38" t="n">
         <v>1.2</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -3921,7 +4904,7 @@
           <t>ความหนา (ซม.)</t>
         </is>
       </c>
-      <c r="B23" s="36">
+      <c r="B23" s="39">
         <f>B16/10</f>
         <v/>
       </c>
@@ -3945,7 +4928,7 @@
           <t>ราคาต้นทุน/แผ่น (บาท)</t>
         </is>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="40">
         <f>B24/1000*B18</f>
         <v/>
       </c>
@@ -3957,7 +4940,7 @@
           <t>ราคาขาย/แผ่น (+กำไร) (บาท)</t>
         </is>
       </c>
-      <c r="B26" s="38">
+      <c r="B26" s="41">
         <f>B25*(1+B20/100)</f>
         <v/>
       </c>
@@ -3993,7 +4976,7 @@
           <t>ราคาขายรวม (บาท)</t>
         </is>
       </c>
-      <c r="B29" s="39">
+      <c r="B29" s="42">
         <f>B26*B19</f>
         <v/>
       </c>
@@ -4144,7 +5127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4664,388 +5647,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Quick Select — แนะนำเครื่อง / วิธีพิมพ์ / จำนวนสี</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1. แนะนำวิธีพิมพ์ตามจำนวนสั่ง</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>จำนวนสั่ง</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>วิธีแนะนำ</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>เหตุผล</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>&lt; 500 ชิ้น</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Work-and-Turn</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ค่าเพลทประหยัดครึ่งหนึ่ง</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>500–2,000 ชิ้น</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Work-and-Turn</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ยังประหยัดได้ชัดเจน</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2,001–5,000 ชิ้น</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Work-and-Turn / Sheetwise</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>พิจารณาตามคุณภาพ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>&gt; 5,000 ชิ้น</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Sheetwise</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Registration ดีกว่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2. แนะนำเครื่องตามจำนวนสี</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>งาน</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>เครื่องที่แนะนำ</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>หมายเหตุ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>1–2 สี</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>GTO52, MO</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>4 สี (CMYK)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>GTO52, MO, SM74, XL106</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>5+ สี + Pantone/Coating</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>GTO52, MO, SM74</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>5+ unit</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>พิมพ์ 2 ด้านรอบเดียว</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>MOVP, SM74-2P, XL106-2P</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Perfector</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>3. แนะนำเครื่องตามขนาดกระดาษ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>กระดาษ</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>เครื่องที่รองรับ</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>หมายเหตุ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>≤ 36×52 ซม. (A3+)</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>GTO 46, GTO 52, SM52</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>งานเล็ก ปริมาณน้อย</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>≤ 48×65 ซม.</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>MO / MOVP</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>B2 นิยมในไทย (ตัด 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>≤ 52×74 ซม.</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>SX52</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>24"×35" หรือ 25"×36"</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>SM74 / CD102 / XL106</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>เหมาะงาน A4 ไม่เสียเศษ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>≤ 53×74 ซม.</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>SM74 / SX74</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>B2+ สมรรถนะสูง</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>≤ 53×75 ซม.</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>XL75</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>B2+ XL series</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>≤ 72×102 ซม.</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>CD102 / SX102</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>≤ 75×106 ซม.</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>XL106 / Komori S40</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>B1 สมรรถนะสูงสุด</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ งาน A4 ห้ามใช้กระดาษ 31×43 (เสียเศษมาก) — ใช้ 24×35 หรือ 25×36 แทน</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A30:C30"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>